--- a/Projecten-Leerjaar2/bas/requirements-planning/burndown.xlsx
+++ b/Projecten-Leerjaar2/bas/requirements-planning/burndown.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ace\Desktop\Projecten2\Projecten-Leerjaar2\bas\requirements-planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41AAD023-15E0-4285-9A2F-6C80DB534C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2ADC7C-4417-4312-B83D-A79B525356F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10830" yWindow="2325" windowWidth="28800" windowHeight="15345" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
+    <workbookView xWindow="21030" yWindow="1740" windowWidth="26730" windowHeight="15345" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
   </bookViews>
   <sheets>
     <sheet name="BurndownChart" sheetId="2" r:id="rId1"/>
@@ -584,22 +584,22 @@
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>40</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>40</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>40</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>40</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2119,7 +2119,9 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>32</v>
       </c>
@@ -2137,7 +2139,9 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
       <c r="F13" s="2" t="s">
         <v>32</v>
       </c>
@@ -2582,32 +2586,32 @@
         <v>40</v>
       </c>
       <c r="D41" s="7">
-        <f t="shared" ref="C41:H41" si="0">C$41-SUM(D3:D40)</f>
+        <f t="shared" ref="D41:H41" si="0">C$41-SUM(D3:D40)</f>
         <v>40</v>
       </c>
       <c r="E41" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F41" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I41" s="7">
         <f t="shared" ref="I41:J41" si="1">H$41-SUM(I3:I40)</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J41" s="7">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2660,6 +2664,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7EB66B5F93AD54F88C68A8B3F2870BB" ma:contentTypeVersion="17" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8c2a24a36bb82fd1af5ed8c009a064aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2982a79d-ff19-4d7a-967e-033e92b0df6e" xmlns:ns3="b123560b-c09d-4726-86a8-96759d196851" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c02a383944889dc160483fd1e510a099" ns2:_="" ns3:_="">
     <xsd:import namespace="2982a79d-ff19-4d7a-967e-033e92b0df6e"/>
@@ -2908,16 +2921,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E3F4124-1599-40F1-988E-E24419BF3D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2934,12 +2946,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Projecten-Leerjaar2/bas/requirements-planning/burndown.xlsx
+++ b/Projecten-Leerjaar2/bas/requirements-planning/burndown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ace\Desktop\Projecten2\Projecten-Leerjaar2\bas\requirements-planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2ADC7C-4417-4312-B83D-A79B525356F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F9E9BA-6B5F-4700-9EA1-60ABBDECB86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21030" yWindow="1740" windowWidth="26730" windowHeight="15345" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
   </bookViews>
   <sheets>
     <sheet name="BurndownChart" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>Taak</t>
   </si>
@@ -174,6 +174,15 @@
   </si>
   <si>
     <t>wireframe insert klant</t>
+  </si>
+  <si>
+    <t>Zoeken</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>Delete</t>
   </si>
 </sst>
 </file>
@@ -587,19 +596,19 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>36</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>36</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>36</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2122,8 +2131,8 @@
       <c r="E12" s="2">
         <v>2</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>32</v>
+      <c r="F12" s="2">
+        <v>2</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -2142,8 +2151,8 @@
       <c r="E13" s="2">
         <v>2</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>32</v>
+      <c r="F13" s="2">
+        <v>2</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -2166,7 +2175,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
@@ -2174,8 +2183,8 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
-        <v>32</v>
+      <c r="F15" s="2">
+        <v>2</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -2198,7 +2207,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
@@ -2206,8 +2215,8 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
-        <v>32</v>
+      <c r="F17" s="2">
+        <v>2</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -2230,7 +2239,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -2238,8 +2247,8 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2" t="s">
-        <v>32</v>
+      <c r="F19" s="2">
+        <v>2</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2595,23 +2604,23 @@
       </c>
       <c r="F41" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I41" s="7">
         <f t="shared" ref="I41:J41" si="1">H$41-SUM(I3:I40)</f>
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J41" s="7">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2664,15 +2673,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7EB66B5F93AD54F88C68A8B3F2870BB" ma:contentTypeVersion="17" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8c2a24a36bb82fd1af5ed8c009a064aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2982a79d-ff19-4d7a-967e-033e92b0df6e" xmlns:ns3="b123560b-c09d-4726-86a8-96759d196851" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c02a383944889dc160483fd1e510a099" ns2:_="" ns3:_="">
     <xsd:import namespace="2982a79d-ff19-4d7a-967e-033e92b0df6e"/>
@@ -2921,15 +2921,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E3F4124-1599-40F1-988E-E24419BF3D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2946,4 +2947,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Projecten-Leerjaar2/bas/requirements-planning/burndown.xlsx
+++ b/Projecten-Leerjaar2/bas/requirements-planning/burndown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ace\Desktop\Projecten2\Projecten-Leerjaar2\bas\requirements-planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F9E9BA-6B5F-4700-9EA1-60ABBDECB86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0344D9-96BC-4382-BDBE-78592D38B4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
   <si>
     <t>Taak</t>
   </si>
@@ -183,6 +183,21 @@
   </si>
   <si>
     <t>Delete</t>
+  </si>
+  <si>
+    <t>Artikelen tonen (SELECT)</t>
+  </si>
+  <si>
+    <t>Artikelen aanmaken(INSERT)</t>
+  </si>
+  <si>
+    <t>Artikel bijwerken (UPDATE)</t>
+  </si>
+  <si>
+    <t>Artikel verwijderen (DELETE)</t>
+  </si>
+  <si>
+    <t>Maak PHPUNIT-testen.</t>
   </si>
 </sst>
 </file>
@@ -599,16 +614,16 @@
                   <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>26</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>26</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>26</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2272,7 +2287,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
@@ -2280,8 +2295,8 @@
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="G21" s="2" t="s">
-        <v>32</v>
+      <c r="G21" s="2">
+        <v>2</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2303,7 +2318,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
@@ -2311,8 +2326,8 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="G23" s="2" t="s">
-        <v>32</v>
+      <c r="G23" s="2">
+        <v>2</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -2320,7 +2335,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
@@ -2328,8 +2343,8 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="G24" s="2" t="s">
-        <v>32</v>
+      <c r="G24" s="2">
+        <v>2</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -2351,7 +2366,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
@@ -2359,8 +2374,8 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="G26" s="2" t="s">
-        <v>32</v>
+      <c r="G26" s="2">
+        <v>2</v>
       </c>
       <c r="H26" s="2"/>
       <c r="J26" s="16"/>
@@ -2381,7 +2396,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B28" s="1">
         <v>2</v>
@@ -2389,8 +2404,8 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="G28" s="2" t="s">
-        <v>32</v>
+      <c r="G28" s="2">
+        <v>2</v>
       </c>
       <c r="H28" s="2"/>
       <c r="J28" s="16"/>
@@ -2608,19 +2623,19 @@
       </c>
       <c r="G41" s="7">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I41" s="7">
         <f t="shared" ref="I41:J41" si="1">H$41-SUM(I3:I40)</f>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J41" s="7">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2673,6 +2688,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7EB66B5F93AD54F88C68A8B3F2870BB" ma:contentTypeVersion="17" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8c2a24a36bb82fd1af5ed8c009a064aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2982a79d-ff19-4d7a-967e-033e92b0df6e" xmlns:ns3="b123560b-c09d-4726-86a8-96759d196851" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c02a383944889dc160483fd1e510a099" ns2:_="" ns3:_="">
     <xsd:import namespace="2982a79d-ff19-4d7a-967e-033e92b0df6e"/>
@@ -2921,16 +2945,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E3F4124-1599-40F1-988E-E24419BF3D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2947,12 +2970,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>